--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487564_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487564_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2781</v>
+        <v>5.3601</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0915</v>
+        <v>7.2701</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.8134</v>
+        <v>-1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1896</v>
+        <v>2.045</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3409</v>
+        <v>1.9438</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.1513</v>
+        <v>0.1012</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7823</v>
+        <v>4.5044</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5398</v>
+        <v>2.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2425</v>
+        <v>1.9544</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5927</v>
+        <v>-2.4594</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.199</v>
+        <v>-0.6062</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3938</v>
+        <v>-1.8532</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1543</v>
+        <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>4.479</v>
+        <v>-0.2553</v>
       </c>
       <c r="T2" t="n">
-        <v>5.4208</v>
+        <v>0.5617</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9418</v>
+        <v>-0.8169</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6071</v>
+        <v>3.3745</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8260999999999999</v>
+        <v>5.1418</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4332</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6633</v>
+        <v>4.4232</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5733</v>
+        <v>8.183199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.91</v>
+        <v>-3.7599</v>
       </c>
       <c r="G3" t="n">
-        <v>2.045</v>
+        <v>5.1896</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9438</v>
+        <v>7.3409</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1012</v>
+        <v>-2.1513</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5044</v>
+        <v>7.7823</v>
       </c>
       <c r="K3" t="n">
-        <v>2.55</v>
+        <v>7.5398</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9544</v>
+        <v>0.2425</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4594</v>
+        <v>-2.5927</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6062</v>
+        <v>-0.199</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8532</v>
+        <v>-2.3938</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1336</v>
+        <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.952</v>
+        <v>1.6241</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1351</v>
+        <v>2.5125</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8169</v>
+        <v>-0.8884</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3745</v>
+        <v>-1.6071</v>
       </c>
       <c r="W3" t="n">
-        <v>5.1418</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7673</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2198</v>
+        <v>1.7629</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3649</v>
+        <v>1.0149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8549</v>
+        <v>0.748</v>
       </c>
       <c r="G4" t="n">
         <v>2.7421</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2403</v>
+        <v>0.7834</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9663</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.274</v>
+        <v>0.167</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1883</v>
+        <v>0.6976</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1831</v>
+        <v>1.8527</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9948</v>
+        <v>-1.1551</v>
       </c>
       <c r="G5" t="n">
         <v>0.2028</v>
@@ -844,13 +844,13 @@
         <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0651</v>
+        <v>0.5743</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5554</v>
+        <v>1.2251</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4904</v>
+        <v>-0.6508</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2754</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4064</v>
+        <v>-0.9979</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3582</v>
+        <v>-0.4845</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0481</v>
+        <v>-0.5134</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5389</v>
+        <v>-1.3643</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.9783</v>
+        <v>-0.6468</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4394</v>
+        <v>-0.7175</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7348</v>
+        <v>-0.4945</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9617</v>
+        <v>-0.5802</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2269</v>
+        <v>0.0857</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8041</v>
+        <v>-0.8698</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0166</v>
+        <v>-0.0667</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7875</v>
+        <v>-0.8031</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3502</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5517</v>
+        <v>-0.0253</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2329</v>
+        <v>0.01</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3188</v>
+        <v>-0.0353</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4118</v>
+        <v>-1.0224</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7915</v>
+        <v>-0.7872</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6203</v>
+        <v>-0.2352</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3643</v>
+        <v>-2.5389</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6468</v>
+        <v>-2.9783</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7175</v>
+        <v>0.4394</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4945</v>
+        <v>-0.7348</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5802</v>
+        <v>-1.9617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0857</v>
+        <v>1.2269</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8698</v>
+        <v>-1.8041</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0667</v>
+        <v>-1.0166</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8031</v>
+        <v>-0.7875</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>2.3502</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4392</v>
+        <v>-0.1678</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.297</v>
+        <v>0.3382</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1422</v>
+        <v>-0.5059</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9566</v>
+        <v>-1.4717</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6646</v>
+        <v>1.1763</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6212</v>
+        <v>-2.6479</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3673</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9971</v>
+        <v>-0.5121</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.594</v>
+        <v>-0.0823</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.403</v>
+        <v>-0.4298</v>
       </c>
       <c r="V8" t="n">
         <v>-1.159</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0618</v>
+        <v>-1.7683</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1007</v>
+        <v>0.2536</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1625</v>
+        <v>-2.0218</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0085</v>
+        <v>-3.1613</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3062</v>
+        <v>-0.9381</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7023</v>
+        <v>-2.2232</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1425</v>
+        <v>-0.8373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1021</v>
+        <v>-0.7401</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.151</v>
+        <v>-2.324</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4083</v>
+        <v>-0.1979</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7427</v>
+        <v>-2.1261</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7419</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0533</v>
+        <v>-0.3696</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0418</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0115</v>
+        <v>-0.9478</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7369</v>
+        <v>-1.9106</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3409</v>
+        <v>0.3054</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.396</v>
+        <v>-2.216</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1613</v>
+        <v>-2.0085</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9381</v>
+        <v>-0.3062</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2232</v>
+        <v>-1.7023</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8373</v>
+        <v>0.1425</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7401</v>
+        <v>0.1021</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.0404</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.324</v>
+        <v>-2.151</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1979</v>
+        <v>-0.4083</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1261</v>
+        <v>-1.7427</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7419</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3383</v>
+        <v>0.0979</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0163</v>
+        <v>0.1629</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.322</v>
+        <v>-0.065</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.775999999999998</v>
+        <v>5.072900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>18.4875</v>
+        <v>18.7845</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.7114</v>
+        <v>-13.7113</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2607999999999993</v>
+        <v>-0.2607999999999984</v>
       </c>
       <c r="H11" t="n">
         <v>6.457800000000002</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.7187</v>
+        <v>-6.718699999999999</v>
       </c>
       <c r="J11" t="n">
         <v>16.0516</v>
@@ -1312,22 +1312,22 @@
         <v>15.6679</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4528</v>
+        <v>1.7496</v>
       </c>
       <c r="T11" t="n">
-        <v>5.6254</v>
+        <v>5.9226</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.1726</v>
+        <v>-4.1729</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3329</v>
       </c>
       <c r="W11" t="n">
-        <v>8.561399999999999</v>
+        <v>8.561400000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.894300000000001</v>
+        <v>-8.894299999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.5227</v>
+        <v>4.005</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9154</v>
+        <v>4.7664</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3927</v>
+        <v>-0.7614</v>
       </c>
       <c r="G12" t="n">
         <v>0.4548</v>
@@ -1390,13 +1390,13 @@
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5552</v>
+        <v>1.0375</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7064</v>
+        <v>1.5574</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1513</v>
+        <v>-0.5199</v>
       </c>
       <c r="V12" t="n">
         <v>2.7086</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5356</v>
+        <v>3.381</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5649</v>
+        <v>6.9743</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0293</v>
+        <v>-3.5932</v>
       </c>
       <c r="G13" t="n">
         <v>3.7836</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3643</v>
+        <v>-0.5189</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0129</v>
+        <v>0.3964</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3514</v>
+        <v>-0.9153</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2754</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9684</v>
+        <v>2.1942</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0011</v>
+        <v>1.7965</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0328</v>
+        <v>0.3977</v>
       </c>
       <c r="G14" t="n">
         <v>1.7448</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4977</v>
+        <v>0.7236</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0369</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5391</v>
+        <v>-0.1087</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6659</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9407</v>
+        <v>1.3939</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0508</v>
+        <v>0.9243</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1101</v>
+        <v>0.4696</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6703</v>
+        <v>0.279</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9381</v>
+        <v>0.2998</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7323</v>
+        <v>-0.0208</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3985</v>
+        <v>0.8842</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6006</v>
+        <v>0.9101</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2021</v>
+        <v>-0.026</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2718</v>
+        <v>-0.6052</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3375</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9344</v>
+        <v>0.0052</v>
       </c>
       <c r="P15" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1958</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3709</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.3355</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.0394</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.2961</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.9792</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.611</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.212</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.3991</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2166</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7265</v>
+        <v>-0.2107</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3103</v>
+        <v>1.0275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4162</v>
+        <v>-1.2382</v>
       </c>
       <c r="G16" t="n">
-        <v>0.279</v>
+        <v>-1.6703</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2998</v>
+        <v>-0.9381</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0208</v>
+        <v>-0.7323</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8842</v>
+        <v>-0.3985</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9101</v>
+        <v>-0.6006</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.026</v>
+        <v>0.2021</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6052</v>
+        <v>-1.2718</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.3375</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0052</v>
+        <v>-0.9344</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.003</v>
+        <v>1.4596</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6534</v>
+        <v>1.1886</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3496</v>
+        <v>0.271</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.816</v>
+        <v>-0.6111</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4225</v>
+        <v>2.0365</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2384</v>
+        <v>-2.6475</v>
       </c>
       <c r="G17" t="n">
         <v>1.0564</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6973</v>
+        <v>-0.4924</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6358</v>
+        <v>-0.0218</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0615</v>
+        <v>-0.4707</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2287</v>
+        <v>-1.9217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1747</v>
+        <v>0.4817</v>
       </c>
       <c r="F18" t="n">
         <v>-2.4034</v>
@@ -1858,10 +1858,10 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6581</v>
+        <v>-0.3511</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.297</v>
+        <v>0.01</v>
       </c>
       <c r="U18" t="n">
         <v>-0.3611</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.2096</v>
+        <v>-4.6479</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.9044</v>
+        <v>-4.7787</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3053</v>
+        <v>0.1308</v>
       </c>
       <c r="G19" t="n">
         <v>-4.0036</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.13</v>
+        <v>-0.5683</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3486</v>
+        <v>-0.2229</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7814</v>
+        <v>-0.3454</v>
       </c>
       <c r="V19" t="n">
         <v>1.8825</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.2156</v>
+        <v>-6.3121</v>
       </c>
       <c r="E20" t="n">
-        <v>0.176</v>
+        <v>0.483</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.3916</v>
+        <v>-6.7952</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7559</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2638</v>
+        <v>-0.3604</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1653</v>
+        <v>0.4723</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4291</v>
+        <v>-0.8326</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0415</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.775999999999998</v>
+        <v>-2.729399999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>13.7113</v>
+        <v>13.7115</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.4874</v>
+        <v>-16.4408</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2606999999999995</v>
+        <v>0.2607000000000004</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.457800000000001</v>
+        <v>-6.457799999999999</v>
       </c>
       <c r="I21" t="n">
         <v>6.7184</v>
@@ -2092,13 +2092,13 @@
         <v>11.7507</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.452600000000001</v>
+        <v>0.5941000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>4.172899999999999</v>
+        <v>4.1728</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.625400000000001</v>
+        <v>-3.5788</v>
       </c>
       <c r="V21" t="n">
         <v>0.3330000000000002</v>
